--- a/artfynd/A 22410-2021 artfynd.xlsx
+++ b/artfynd/A 22410-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22410-2021 artfynd.xlsx
+++ b/artfynd/A 22410-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,141 +925,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>81148234</v>
-      </c>
-      <c r="B4" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221343</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Trifolium spadiceum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kustjärnen, 300 m NO om, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>452125.560029934</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6666145.020478152</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Filipstad</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Rämmen</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>S-Fil-0187</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Fuktigt vägdike</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Jan Teodorsson, Johanne Maad, Karin Martinsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
